--- a/validation/exp9_boris/results/all_batches_results.xlsx
+++ b/validation/exp9_boris/results/all_batches_results.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="M2">
-        <v>0.08501431322675891</v>
+        <v>0.1133524176356785</v>
       </c>
       <c r="N2">
         <v>11</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="M3">
-        <v>0.03201088303168734</v>
+        <v>0.06402176606337467</v>
       </c>
       <c r="N3">
         <v>11</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M5">
-        <v>0.08501431322675891</v>
+        <v>0.1133524176356785</v>
       </c>
       <c r="N5">
         <v>11</v>
@@ -766,19 +766,19 @@
         <v>93</v>
       </c>
       <c r="G8">
-        <v>0.1207362841138933</v>
+        <v>0.06714071624716159</v>
       </c>
       <c r="H8">
-        <v>0.6733485374503095</v>
+        <v>0.4405619777979101</v>
       </c>
       <c r="I8">
-        <v>0.2112999839614958</v>
+        <v>-0.02148657569090364</v>
       </c>
       <c r="J8">
-        <v>1.135397090939123</v>
+        <v>0.9026105312867239</v>
       </c>
       <c r="K8">
-        <v>0.004672267809869151</v>
+        <v>0.06144126038887604</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M8">
-        <v>0.03201088303168734</v>
+        <v>0.1436995696814379</v>
       </c>
       <c r="N8">
         <v>11</v>
@@ -818,19 +818,19 @@
         <v>93</v>
       </c>
       <c r="G9">
-        <v>-0.006785933429388841</v>
+        <v>-0.006400451383782231</v>
       </c>
       <c r="H9">
-        <v>-0.02632013678492536</v>
+        <v>-0.02483364900460195</v>
       </c>
       <c r="I9">
-        <v>-0.4883686902737391</v>
+        <v>-0.4868822024934158</v>
       </c>
       <c r="J9">
-        <v>0.4357284167038884</v>
+        <v>0.4372149044842119</v>
       </c>
       <c r="K9">
-        <v>0.9103168657142213</v>
+        <v>0.9153620368565042</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
         <v>93</v>
       </c>
       <c r="E13">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G13">
-        <v>0.01519559416331258</v>
+        <v>0.02289732811964476</v>
       </c>
       <c r="H13">
-        <v>0.2056115766165126</v>
+        <v>0.3117763169211952</v>
       </c>
       <c r="I13">
-        <v>-0.2558985978551914</v>
+        <v>-0.1400463604782532</v>
       </c>
       <c r="J13">
-        <v>0.6671217510882165</v>
+        <v>0.7635989943206437</v>
       </c>
       <c r="K13">
-        <v>0.3782691358385621</v>
+        <v>0.1737072849770679</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M13">
-        <v>0.5944229277463119</v>
+        <v>0.2811892457359251</v>
       </c>
       <c r="N13">
         <v>11</v>
@@ -1072,25 +1072,25 @@
         <v>93</v>
       </c>
       <c r="E14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G14">
-        <v>4.071382588517079</v>
+        <v>8.584617592193979</v>
       </c>
       <c r="H14">
-        <v>0.2085820151955507</v>
+        <v>0.4475089405134678</v>
       </c>
       <c r="I14">
-        <v>-0.2529281592761533</v>
+        <v>-0.004313736885980603</v>
       </c>
       <c r="J14">
-        <v>0.6700921896672547</v>
+        <v>0.8993316179129163</v>
       </c>
       <c r="K14">
-        <v>0.3714502509484889</v>
+        <v>0.05217834543350618</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="M14">
-        <v>0.5944229277463119</v>
+        <v>0.1956502078310902</v>
       </c>
       <c r="N14">
         <v>11</v>
@@ -1124,25 +1124,25 @@
         <v>93</v>
       </c>
       <c r="E15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F15">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G15">
-        <v>-0.200089827082872</v>
+        <v>0.05660783469651184</v>
       </c>
       <c r="H15">
-        <v>-0.03412448450132367</v>
+        <v>0.009653118570442968</v>
       </c>
       <c r="I15">
-        <v>-0.4956346589730277</v>
+        <v>-0.4421695588290054</v>
       </c>
       <c r="J15">
-        <v>0.4273856899703803</v>
+        <v>0.4614757959698914</v>
       </c>
       <c r="K15">
-        <v>0.8834842116510848</v>
+        <v>0.9662209711535699</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="M15">
-        <v>0.8834842116510848</v>
+        <v>0.9662209711535699</v>
       </c>
       <c r="N15">
         <v>11</v>
@@ -1176,25 +1176,25 @@
         <v>93</v>
       </c>
       <c r="E16">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G16">
-        <v>39.56594517362534</v>
+        <v>97.38950112034983</v>
       </c>
       <c r="H16">
-        <v>0.1560753949145451</v>
+        <v>0.3896586509594753</v>
       </c>
       <c r="I16">
-        <v>-0.3054347795571589</v>
+        <v>-0.06216402643997309</v>
       </c>
       <c r="J16">
-        <v>0.6175855693862492</v>
+        <v>0.8414813283589236</v>
       </c>
       <c r="K16">
-        <v>0.5032028013527373</v>
+        <v>0.09005267003375779</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="M16">
-        <v>0.613745844507223</v>
+        <v>0.2476448425928339</v>
       </c>
       <c r="N16">
         <v>11</v>
@@ -1228,25 +1228,25 @@
         <v>92</v>
       </c>
       <c r="E17">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G17">
-        <v>-0.1590767094656389</v>
+        <v>-0.161300334277039</v>
       </c>
       <c r="H17">
-        <v>-0.6741524908503982</v>
+        <v>-0.6860428340463276</v>
       </c>
       <c r="I17">
-        <v>-1.138670216172327</v>
+        <v>-1.140689678068461</v>
       </c>
       <c r="J17">
-        <v>-0.2096347655284691</v>
+        <v>-0.2313959900241943</v>
       </c>
       <c r="K17">
-        <v>0.004951000691451968</v>
+        <v>0.003539592810587274</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="M17">
-        <v>0.05446100760597165</v>
+        <v>0.03893552091646001</v>
       </c>
       <c r="N17">
         <v>11</v>
@@ -1280,25 +1280,25 @@
         <v>93</v>
       </c>
       <c r="E18">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F18">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G18">
-        <v>-5.771532300321884</v>
+        <v>-5.102833979050073</v>
       </c>
       <c r="H18">
-        <v>-0.5061397491218675</v>
+        <v>-0.4452343263094108</v>
       </c>
       <c r="I18">
-        <v>-0.9676499235935715</v>
+        <v>-0.8970570037088592</v>
       </c>
       <c r="J18">
-        <v>-0.04462957465016358</v>
+        <v>0.006588351090037589</v>
       </c>
       <c r="K18">
-        <v>0.03197650584857299</v>
+        <v>0.05335914759029734</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M18">
-        <v>0.1758707821671515</v>
+        <v>0.1956502078310902</v>
       </c>
       <c r="N18">
         <v>11</v>
@@ -1332,25 +1332,25 @@
         <v>93</v>
       </c>
       <c r="E19">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G19">
-        <v>-0.01955974549781864</v>
+        <v>-0.02915969001335296</v>
       </c>
       <c r="H19">
-        <v>-0.1365500805604654</v>
+        <v>-0.2041111658505001</v>
       </c>
       <c r="I19">
-        <v>-0.5980602550321693</v>
+        <v>-0.6559338432499485</v>
       </c>
       <c r="J19">
-        <v>0.3249600939112386</v>
+        <v>0.2477115115489483</v>
       </c>
       <c r="K19">
-        <v>0.5579507677338391</v>
+        <v>0.3716660196807224</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="M19">
-        <v>0.613745844507223</v>
+        <v>0.5110407770609934</v>
       </c>
       <c r="N19">
         <v>11</v>
@@ -1384,25 +1384,25 @@
         <v>93</v>
       </c>
       <c r="E20">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G20">
-        <v>-0.04072088313022296</v>
+        <v>-0.00626646768769981</v>
       </c>
       <c r="H20">
-        <v>-0.1562438797038029</v>
+        <v>-0.02398258911919281</v>
       </c>
       <c r="I20">
-        <v>-0.6177540541755069</v>
+        <v>-0.4758052665186412</v>
       </c>
       <c r="J20">
-        <v>0.3052662947679012</v>
+        <v>0.4278400882802555</v>
       </c>
       <c r="K20">
-        <v>0.5027432575122239</v>
+        <v>0.9162098428482601</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="M20">
-        <v>0.613745844507223</v>
+        <v>0.9662209711535699</v>
       </c>
       <c r="N20">
         <v>11</v>
@@ -1436,25 +1436,25 @@
         <v>91</v>
       </c>
       <c r="E21">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G21">
-        <v>-1.153398341440845</v>
+        <v>-1.103575744358542</v>
       </c>
       <c r="H21">
-        <v>-0.3283223346682714</v>
+        <v>-0.313968545412381</v>
       </c>
       <c r="I21">
-        <v>-0.798201162611234</v>
+        <v>-0.7746316821981623</v>
       </c>
       <c r="J21">
-        <v>0.1415564932746911</v>
+        <v>0.1466945913734004</v>
       </c>
       <c r="K21">
-        <v>0.1683474985975603</v>
+        <v>0.1789386109228615</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="M21">
-        <v>0.4629556211432908</v>
+        <v>0.2811892457359251</v>
       </c>
       <c r="N21">
         <v>11</v>
@@ -1488,25 +1488,25 @@
         <v>91</v>
       </c>
       <c r="E22">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F22">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G22">
-        <v>2.52749873433663</v>
+        <v>2.47850550214322</v>
       </c>
       <c r="H22">
-        <v>0.3512374933464477</v>
+        <v>0.3444311935020893</v>
       </c>
       <c r="I22">
-        <v>-0.1186413345965148</v>
+        <v>-0.116231943283692</v>
       </c>
       <c r="J22">
-        <v>0.82111632128941</v>
+        <v>0.8050943302878707</v>
       </c>
       <c r="K22">
-        <v>0.1408911670022441</v>
+        <v>0.140797229817042</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="M22">
-        <v>0.4629556211432908</v>
+        <v>0.2811892457359251</v>
       </c>
       <c r="N22">
         <v>11</v>
@@ -1540,25 +1540,25 @@
         <v>91</v>
       </c>
       <c r="E23">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F23">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G23">
-        <v>-195.6102113118382</v>
+        <v>-120.5736075421049</v>
       </c>
       <c r="H23">
-        <v>-0.2137136955280048</v>
+        <v>-0.1313463546240952</v>
       </c>
       <c r="I23">
-        <v>-0.6835925234709672</v>
+        <v>-0.5920094914098765</v>
       </c>
       <c r="J23">
-        <v>0.2561651324149576</v>
+        <v>0.3293167821616862</v>
       </c>
       <c r="K23">
-        <v>0.3683309674807437</v>
+        <v>0.5722253383519144</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="M23">
-        <v>0.5944229277463119</v>
+        <v>0.6993865246523399</v>
       </c>
       <c r="N23">
         <v>11</v>
@@ -1589,28 +1589,28 @@
         </is>
       </c>
       <c r="D24">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>24</v>
       </c>
       <c r="F24">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G24">
-        <v>0.04437100172332005</v>
+        <v>0.04826649997748613</v>
       </c>
       <c r="H24">
-        <v>0.5479113482978304</v>
+        <v>0.6093470224184824</v>
       </c>
       <c r="I24">
-        <v>0.008758542538902627</v>
+        <v>0.06176451071040267</v>
       </c>
       <c r="J24">
-        <v>1.087064154056758</v>
+        <v>1.156929534126562</v>
       </c>
       <c r="K24">
-        <v>0.04651350775014364</v>
+        <v>0.02987943506650974</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="M24">
-        <v>0.2182628643343841</v>
+        <v>0.1095579285772024</v>
       </c>
       <c r="N24">
         <v>11</v>
@@ -1641,28 +1641,28 @@
         </is>
       </c>
       <c r="D25">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G25">
-        <v>13.79274328420609</v>
+        <v>15.92772901003124</v>
       </c>
       <c r="H25">
-        <v>0.6767225010293841</v>
+        <v>0.8237772563658241</v>
       </c>
       <c r="I25">
-        <v>0.1375696952704564</v>
+        <v>0.2761947446577444</v>
       </c>
       <c r="J25">
-        <v>1.215875306788312</v>
+        <v>1.371359768073904</v>
       </c>
       <c r="K25">
-        <v>0.01482393496255176</v>
+        <v>0.003925929042873044</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="M25">
-        <v>0.1630632845880693</v>
+        <v>0.04318521947160349</v>
       </c>
       <c r="N25">
         <v>11</v>
@@ -1693,28 +1693,28 @@
         </is>
       </c>
       <c r="D26">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E26">
         <v>24</v>
       </c>
       <c r="F26">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G26">
-        <v>2.098071495766698</v>
+        <v>2.180622507885496</v>
       </c>
       <c r="H26">
-        <v>0.3793867753762796</v>
+        <v>0.3929973173747644</v>
       </c>
       <c r="I26">
-        <v>-0.1597660303826481</v>
+        <v>-0.1545851943333153</v>
       </c>
       <c r="J26">
-        <v>0.9185395811352073</v>
+        <v>0.940579829082844</v>
       </c>
       <c r="K26">
-        <v>0.1641801998083072</v>
+        <v>0.1558158189072223</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="M26">
-        <v>0.3528626476000146</v>
+        <v>0.3485910416407478</v>
       </c>
       <c r="N26">
         <v>11</v>
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="D27">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>24</v>
       </c>
       <c r="F27">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G27">
-        <v>132.435641908525</v>
+        <v>165.5080488988319</v>
       </c>
       <c r="H27">
-        <v>0.4809237562054655</v>
+        <v>0.6421424892663681</v>
       </c>
       <c r="I27">
-        <v>-0.05822904955346218</v>
+        <v>0.09455997755828834</v>
       </c>
       <c r="J27">
-        <v>1.020076561964393</v>
+        <v>1.189725000974448</v>
       </c>
       <c r="K27">
-        <v>0.07936831430341242</v>
+        <v>0.02243115626427288</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="M27">
-        <v>0.2182628643343841</v>
+        <v>0.1095579285772024</v>
       </c>
       <c r="N27">
         <v>11</v>
@@ -1797,28 +1797,28 @@
         </is>
       </c>
       <c r="D28">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>24</v>
       </c>
       <c r="F28">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G28">
-        <v>-0.08389511077681858</v>
+        <v>-0.09312397376822193</v>
       </c>
       <c r="H28">
-        <v>-0.3566984237544505</v>
+        <v>-0.3923478690519177</v>
       </c>
       <c r="I28">
-        <v>-0.8984512233319308</v>
+        <v>-0.942675367532973</v>
       </c>
       <c r="J28">
-        <v>0.1850543758230297</v>
+        <v>0.1579796294291377</v>
       </c>
       <c r="K28">
-        <v>0.1924705350545534</v>
+        <v>0.1584504734730672</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M28">
-        <v>0.3528626476000146</v>
+        <v>0.3485910416407478</v>
       </c>
       <c r="N28">
         <v>11</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="D29">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>24</v>
       </c>
       <c r="F29">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G29">
-        <v>-2.931514581373459</v>
+        <v>-2.867176496260569</v>
       </c>
       <c r="H29">
-        <v>-0.3011066940736311</v>
+        <v>-0.2848581437500901</v>
       </c>
       <c r="I29">
-        <v>-0.8402594998325589</v>
+        <v>-0.8324406554581698</v>
       </c>
       <c r="J29">
-        <v>0.2380461116852967</v>
+        <v>0.2627243679579897</v>
       </c>
       <c r="K29">
-        <v>0.2680134403797476</v>
+        <v>0.3013702413840724</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="M29">
-        <v>0.4211639777396034</v>
+        <v>0.4688445860254871</v>
       </c>
       <c r="N29">
         <v>11</v>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="D30">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>23</v>
       </c>
       <c r="F30">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G30">
-        <v>0.09914571935849043</v>
+        <v>0.05312458313744517</v>
       </c>
       <c r="H30">
-        <v>0.4968443794342607</v>
+        <v>0.3189302287555219</v>
       </c>
       <c r="I30">
-        <v>-0.05464228611951752</v>
+        <v>-0.2398164103865086</v>
       </c>
       <c r="J30">
-        <v>1.048331044988039</v>
+        <v>0.8776768678975525</v>
       </c>
       <c r="K30">
-        <v>0.07647370623507579</v>
+        <v>0.2571766374667313</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="M30">
-        <v>0.2182628643343841</v>
+        <v>0.4688445860254871</v>
       </c>
       <c r="N30">
         <v>11</v>
@@ -1953,28 +1953,28 @@
         </is>
       </c>
       <c r="D31">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <v>23</v>
       </c>
       <c r="F31">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G31">
-        <v>-0.0221748655878836</v>
+        <v>-0.007994812520945322</v>
       </c>
       <c r="H31">
-        <v>-0.09476376059886797</v>
+        <v>-0.0346059011467369</v>
       </c>
       <c r="I31">
-        <v>-0.6462504261526463</v>
+        <v>-0.5933525402887675</v>
       </c>
       <c r="J31">
-        <v>0.4567229049549104</v>
+        <v>0.5241407379952937</v>
       </c>
       <c r="K31">
-        <v>0.7318876196265927</v>
+        <v>0.9015353085128233</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="M31">
-        <v>0.7318876196265927</v>
+        <v>0.9015353085128233</v>
       </c>
       <c r="N31">
         <v>11</v>
@@ -2005,28 +2005,28 @@
         </is>
       </c>
       <c r="D32">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E32">
         <v>22</v>
       </c>
       <c r="F32">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G32">
-        <v>-0.8738223763184577</v>
+        <v>-0.8697518663723902</v>
       </c>
       <c r="H32">
-        <v>-0.2756315959506122</v>
+        <v>-0.2718189261208896</v>
       </c>
       <c r="I32">
-        <v>-0.8380837624221419</v>
+        <v>-0.8397040227039787</v>
       </c>
       <c r="J32">
-        <v>0.2868205705209176</v>
+        <v>0.2960661704621995</v>
       </c>
       <c r="K32">
-        <v>0.3301113930012022</v>
+        <v>0.3409778807458088</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="M32">
-        <v>0.453903165376653</v>
+        <v>0.4688445860254871</v>
       </c>
       <c r="N32">
         <v>11</v>
@@ -2057,28 +2057,28 @@
         </is>
       </c>
       <c r="D33">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E33">
         <v>22</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G33">
-        <v>-1.862981870918736</v>
+        <v>-1.736474713938851</v>
       </c>
       <c r="H33">
-        <v>-0.2385460751275745</v>
+        <v>-0.2205983828592166</v>
       </c>
       <c r="I33">
-        <v>-0.8009982415991043</v>
+        <v>-0.7884834794423058</v>
       </c>
       <c r="J33">
-        <v>0.3239060913439551</v>
+        <v>0.3472867137238727</v>
       </c>
       <c r="K33">
-        <v>0.3987779935591211</v>
+        <v>0.4389296055057578</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M33">
-        <v>0.4873953254611481</v>
+        <v>0.5364695178403707</v>
       </c>
       <c r="N33">
         <v>11</v>
@@ -2109,28 +2109,28 @@
         </is>
       </c>
       <c r="D34">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E34">
         <v>22</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G34">
-        <v>136.8646317183513</v>
+        <v>166.65394480995</v>
       </c>
       <c r="H34">
-        <v>0.1455554966738113</v>
+        <v>0.1759543150738717</v>
       </c>
       <c r="I34">
-        <v>-0.4168966697977184</v>
+        <v>-0.3919307815092176</v>
       </c>
       <c r="J34">
-        <v>0.7080076631453411</v>
+        <v>0.743839411656961</v>
       </c>
       <c r="K34">
-        <v>0.6058785421020172</v>
+        <v>0.5365496695846979</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="M34">
-        <v>0.6664663963122189</v>
+        <v>0.5902046365431677</v>
       </c>
       <c r="N34">
         <v>11</v>
@@ -2161,28 +2161,28 @@
         </is>
       </c>
       <c r="D35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E35">
         <v>24</v>
       </c>
       <c r="F35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G35">
-        <v>0.03547313223364898</v>
+        <v>0.03070908131374459</v>
       </c>
       <c r="H35">
-        <v>0.5564992230321598</v>
+        <v>0.4733649834777794</v>
       </c>
       <c r="I35">
-        <v>0.05944752886453677</v>
+        <v>-0.01352140033195895</v>
       </c>
       <c r="J35">
-        <v>1.053550917199783</v>
+        <v>0.9602513672875178</v>
       </c>
       <c r="K35">
-        <v>0.02874273227742575</v>
+        <v>0.05653917068926837</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="M35">
-        <v>0.0790425137629208</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N35">
         <v>11</v>
@@ -2213,28 +2213,28 @@
         </is>
       </c>
       <c r="D36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E36">
         <v>24</v>
       </c>
       <c r="F36">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G36">
-        <v>10.99660808266138</v>
+        <v>9.101800881875125</v>
       </c>
       <c r="H36">
-        <v>0.6373312966419847</v>
+        <v>0.5169658946275346</v>
       </c>
       <c r="I36">
-        <v>0.1402796024743616</v>
+        <v>0.03007951081779624</v>
       </c>
       <c r="J36">
-        <v>1.134382990809608</v>
+        <v>1.003852278437273</v>
       </c>
       <c r="K36">
-        <v>0.01270705450884857</v>
+        <v>0.0377364735219017</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="M36">
-        <v>0.06988879979866715</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N36">
         <v>11</v>
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="D37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E37">
         <v>24</v>
       </c>
       <c r="F37">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G37">
-        <v>2.632707257013181</v>
+        <v>2.43019262009747</v>
       </c>
       <c r="H37">
-        <v>0.4828424469302881</v>
+        <v>0.4467942558870175</v>
       </c>
       <c r="I37">
-        <v>-0.01420924723733507</v>
+        <v>-0.04009212792272075</v>
       </c>
       <c r="J37">
-        <v>0.9798941410979113</v>
+        <v>0.9336806396967559</v>
       </c>
       <c r="K37">
-        <v>0.05673193827130914</v>
+        <v>0.07151657721680629</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="M37">
-        <v>0.1040085534974001</v>
+        <v>0.1573364698769739</v>
       </c>
       <c r="N37">
         <v>11</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="D38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E38">
         <v>24</v>
       </c>
       <c r="F38">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G38">
-        <v>118.5804548804961</v>
+        <v>98.02257850496325</v>
       </c>
       <c r="H38">
-        <v>0.5065439012016414</v>
+        <v>0.4197034671382261</v>
       </c>
       <c r="I38">
-        <v>0.009492207034018253</v>
+        <v>-0.06718291667151226</v>
       </c>
       <c r="J38">
-        <v>1.003595595369265</v>
+        <v>0.9065898509479645</v>
       </c>
       <c r="K38">
-        <v>0.04589415060193286</v>
+        <v>0.09006554760160734</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M38">
-        <v>0.1009671313242523</v>
+        <v>0.1651201706029468</v>
       </c>
       <c r="N38">
         <v>11</v>
@@ -2369,28 +2369,28 @@
         </is>
       </c>
       <c r="D39">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E39">
         <v>24</v>
       </c>
       <c r="F39">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G39">
-        <v>0.05654488213554677</v>
+        <v>0.05541989464635406</v>
       </c>
       <c r="H39">
-        <v>0.2188999448996439</v>
+        <v>0.218182585781288</v>
       </c>
       <c r="I39">
-        <v>-0.2781517492679793</v>
+        <v>-0.2687037980284504</v>
       </c>
       <c r="J39">
-        <v>0.7159516390672669</v>
+        <v>0.7050689695910263</v>
       </c>
       <c r="K39">
-        <v>0.3828372552862699</v>
+        <v>0.3748748589945128</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="M39">
-        <v>0.467912200905441</v>
+        <v>0.4581803832155157</v>
       </c>
       <c r="N39">
         <v>11</v>
@@ -2421,28 +2421,28 @@
         </is>
       </c>
       <c r="D40">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E40">
         <v>24</v>
       </c>
       <c r="F40">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G40">
-        <v>3.556171036325313</v>
+        <v>3.388115958845825</v>
       </c>
       <c r="H40">
-        <v>0.3138350079278913</v>
+        <v>0.3068705228793474</v>
       </c>
       <c r="I40">
-        <v>-0.1832166862397319</v>
+        <v>-0.1800158609303909</v>
       </c>
       <c r="J40">
-        <v>0.8108867020955144</v>
+        <v>0.7937569066890857</v>
       </c>
       <c r="K40">
-        <v>0.2121676449215741</v>
+        <v>0.2131714551096454</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="M40">
-        <v>0.2917305117671645</v>
+        <v>0.2931107507757624</v>
       </c>
       <c r="N40">
         <v>11</v>
@@ -2473,28 +2473,28 @@
         </is>
       </c>
       <c r="D41">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E41">
         <v>23</v>
       </c>
       <c r="F41">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G41">
-        <v>0.1312496070497738</v>
+        <v>0.07533161201871862</v>
       </c>
       <c r="H41">
-        <v>0.6711483926699491</v>
+        <v>0.4910137319917606</v>
       </c>
       <c r="I41">
-        <v>0.1695004090975513</v>
+        <v>-0.002592081012958921</v>
       </c>
       <c r="J41">
-        <v>1.172796376242347</v>
+        <v>0.9846195449964801</v>
       </c>
       <c r="K41">
-        <v>0.009465351071373442</v>
+        <v>0.05118403143498738</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="M41">
-        <v>0.06988879979866715</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N41">
         <v>11</v>
@@ -2525,28 +2525,28 @@
         </is>
       </c>
       <c r="D42">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E42">
         <v>23</v>
       </c>
       <c r="F42">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G42">
-        <v>0.01820117921779418</v>
+        <v>-0.0004109260762045113</v>
       </c>
       <c r="H42">
-        <v>0.06843670692504045</v>
+        <v>-0.00154422686544326</v>
       </c>
       <c r="I42">
-        <v>-0.4332112766473573</v>
+        <v>-0.4951500398701627</v>
       </c>
       <c r="J42">
-        <v>0.5700846904974383</v>
+        <v>0.4920615861392761</v>
       </c>
       <c r="K42">
-        <v>0.7863548185899483</v>
+        <v>0.9950431167164271</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="M42">
-        <v>0.7863548185899483</v>
+        <v>0.9950431167164271</v>
       </c>
       <c r="N42">
         <v>11</v>
@@ -2577,28 +2577,28 @@
         </is>
       </c>
       <c r="D43">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E43">
         <v>22</v>
       </c>
       <c r="F43">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G43">
-        <v>0.6186613956330169</v>
+        <v>0.4787257317160428</v>
       </c>
       <c r="H43">
-        <v>0.1604499623693021</v>
+        <v>0.1254953220585758</v>
       </c>
       <c r="I43">
-        <v>-0.3529395843647835</v>
+        <v>-0.3801389480648064</v>
       </c>
       <c r="J43">
-        <v>0.6738395091033877</v>
+        <v>0.6311295921819581</v>
       </c>
       <c r="K43">
-        <v>0.5349470753598955</v>
+        <v>0.6222096669098827</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="M43">
-        <v>0.5884417828958851</v>
+        <v>0.684430633600871</v>
       </c>
       <c r="N43">
         <v>11</v>
@@ -2629,28 +2629,28 @@
         </is>
       </c>
       <c r="D44">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E44">
         <v>22</v>
       </c>
       <c r="F44">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G44">
-        <v>-4.475711618897693</v>
+        <v>-4.234816817150685</v>
       </c>
       <c r="H44">
-        <v>-0.5773716834864964</v>
+        <v>-0.5491739736872219</v>
       </c>
       <c r="I44">
-        <v>-1.090761230220582</v>
+        <v>-1.054808243810604</v>
       </c>
       <c r="J44">
-        <v>-0.06398213675241078</v>
+        <v>-0.04353970356383965</v>
       </c>
       <c r="K44">
-        <v>0.02808091057709028</v>
+        <v>0.03369928964745056</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="M44">
-        <v>0.0790425137629208</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N44">
         <v>11</v>
@@ -2681,28 +2681,28 @@
         </is>
       </c>
       <c r="D45">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E45">
         <v>22</v>
       </c>
       <c r="F45">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G45">
-        <v>333.7987618001727</v>
+        <v>308.5894220631064</v>
       </c>
       <c r="H45">
-        <v>0.3718106101607991</v>
+        <v>0.3460914124621003</v>
       </c>
       <c r="I45">
-        <v>-0.1415789365732865</v>
+        <v>-0.159542857661282</v>
       </c>
       <c r="J45">
-        <v>0.8852001568948847</v>
+        <v>0.8517256825854826</v>
       </c>
       <c r="K45">
-        <v>0.1530021911830017</v>
+        <v>0.176627456886292</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="M45">
-        <v>0.2404320147161455</v>
+        <v>0.2775574322498874</v>
       </c>
       <c r="N45">
         <v>11</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="M90">
-        <v>0.3377491165742667</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N90">
         <v>11</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="M91">
-        <v>0.1734619372959083</v>
+        <v>0.3469238745918166</v>
       </c>
       <c r="N91">
         <v>11</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="M92">
-        <v>0.3042964754248899</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N92">
         <v>11</v>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="M93">
-        <v>0.3861210256676484</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N93">
         <v>11</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="M95">
-        <v>0.3861210256676484</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N95">
         <v>11</v>
@@ -5342,19 +5342,19 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.1957187609337613</v>
+        <v>0.08418893637299102</v>
       </c>
       <c r="H96">
-        <v>0.8850864177982237</v>
+        <v>0.4687775347318363</v>
       </c>
       <c r="I96">
-        <v>0.2105613513849146</v>
+        <v>-0.2057475316814728</v>
       </c>
       <c r="J96">
-        <v>1.559611484211533</v>
+        <v>1.143302601145145</v>
       </c>
       <c r="K96">
-        <v>0.01109824932238578</v>
+        <v>0.1691523530799554</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="M96">
-        <v>0.1220807425462435</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N96">
         <v>11</v>
@@ -5394,19 +5394,19 @@
         <v>46</v>
       </c>
       <c r="G97">
-        <v>-0.08909018704539848</v>
+        <v>-0.08828801726477908</v>
       </c>
       <c r="H97">
-        <v>-0.3947771883559646</v>
+        <v>-0.3915044597218872</v>
       </c>
       <c r="I97">
-        <v>-1.069302254769274</v>
+        <v>-1.066029526135196</v>
       </c>
       <c r="J97">
-        <v>0.2797478780573444</v>
+        <v>0.2830206066914219</v>
       </c>
       <c r="K97">
-        <v>0.245684530532369</v>
+        <v>0.2495709778114337</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="M97">
-        <v>0.3861210256676484</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N97">
         <v>11</v>
@@ -5596,25 +5596,25 @@
         <v>46</v>
       </c>
       <c r="E101">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F101">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G101">
-        <v>0.02592323580526977</v>
+        <v>0.04005817128712362</v>
       </c>
       <c r="H101">
-        <v>0.3454707593674134</v>
+        <v>0.5452702075255837</v>
       </c>
       <c r="I101">
-        <v>-0.3222949147566656</v>
+        <v>-0.09490695028599257</v>
       </c>
       <c r="J101">
-        <v>1.013236433491493</v>
+        <v>1.18544736533716</v>
       </c>
       <c r="K101">
-        <v>0.3024293571914576</v>
+        <v>0.09299647934519963</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="M101">
-        <v>0.5531547442458277</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N101">
         <v>11</v>
@@ -5648,25 +5648,25 @@
         <v>46</v>
       </c>
       <c r="E102">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F102">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G102">
-        <v>-2.893917274939157</v>
+        <v>6.461551362683461</v>
       </c>
       <c r="H102">
-        <v>-0.1336896830826762</v>
+        <v>0.3011030273145949</v>
       </c>
       <c r="I102">
-        <v>-0.8014553572067552</v>
+        <v>-0.3390741304969815</v>
       </c>
       <c r="J102">
-        <v>0.5340759910414029</v>
+        <v>0.9412801851261712</v>
       </c>
       <c r="K102">
-        <v>0.6882413773292128</v>
+        <v>0.3479534574185675</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="M102">
-        <v>0.757065515062134</v>
+        <v>0.5623900093185237</v>
       </c>
       <c r="N102">
         <v>11</v>
@@ -5700,25 +5700,25 @@
         <v>46</v>
       </c>
       <c r="E103">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F103">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G103">
-        <v>-0.06934306569343023</v>
+        <v>0.420125786163522</v>
       </c>
       <c r="H103">
-        <v>-0.0121456205048761</v>
+        <v>0.07363213986513238</v>
       </c>
       <c r="I103">
-        <v>-0.6799112946289551</v>
+        <v>-0.566545017946444</v>
       </c>
       <c r="J103">
-        <v>0.6556200536192029</v>
+        <v>0.7138092976767089</v>
       </c>
       <c r="K103">
-        <v>0.97089351598039</v>
+        <v>0.8175748503353608</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="M103">
-        <v>0.97089351598039</v>
+        <v>0.8175748503353608</v>
       </c>
       <c r="N103">
         <v>11</v>
@@ -5752,25 +5752,25 @@
         <v>46</v>
       </c>
       <c r="E104">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F104">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G104">
-        <v>138.5605992600366</v>
+        <v>243.1904829874181</v>
       </c>
       <c r="H104">
-        <v>0.5269908246786111</v>
+        <v>0.9985559327746625</v>
       </c>
       <c r="I104">
-        <v>-0.1407748494454679</v>
+        <v>0.3583787749630862</v>
       </c>
       <c r="J104">
-        <v>1.19475649880269</v>
+        <v>1.638733090586239</v>
       </c>
       <c r="K104">
-        <v>0.1187401640394858</v>
+        <v>0.003023888859001053</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="M104">
-        <v>0.4622781207178883</v>
+        <v>0.03326277744901158</v>
       </c>
       <c r="N104">
         <v>11</v>
@@ -5804,25 +5804,25 @@
         <v>46</v>
       </c>
       <c r="E105">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F105">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G105">
-        <v>-0.1070894661822752</v>
+        <v>-0.1155758292170839</v>
       </c>
       <c r="H105">
-        <v>-0.5130962350534849</v>
+        <v>-0.5580435774555059</v>
       </c>
       <c r="I105">
-        <v>-1.180861909177564</v>
+        <v>-1.198220735267082</v>
       </c>
       <c r="J105">
-        <v>0.154669439070594</v>
+        <v>0.08213358035607042</v>
       </c>
       <c r="K105">
-        <v>0.128489258634602</v>
+        <v>0.08583307022047661</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="M105">
-        <v>0.4622781207178883</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N105">
         <v>11</v>
@@ -5856,25 +5856,25 @@
         <v>46</v>
       </c>
       <c r="E106">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F106">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G106">
-        <v>-3.421289537712881</v>
+        <v>-2.308846960167709</v>
       </c>
       <c r="H106">
-        <v>-0.2799656868490875</v>
+        <v>-0.1881269036528407</v>
       </c>
       <c r="I106">
-        <v>-0.9477313609731662</v>
+        <v>-0.828304061464417</v>
       </c>
       <c r="J106">
-        <v>0.3877999872749915</v>
+        <v>0.4520502541587357</v>
       </c>
       <c r="K106">
-        <v>0.402294359451511</v>
+        <v>0.5563295154503705</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="M106">
-        <v>0.5531547442458277</v>
+        <v>0.6799582966615639</v>
       </c>
       <c r="N106">
         <v>11</v>
@@ -5908,25 +5908,25 @@
         <v>46</v>
       </c>
       <c r="E107">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F107">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G107">
-        <v>-0.07222996891840137</v>
+        <v>-0.08666853877123173</v>
       </c>
       <c r="H107">
-        <v>-0.464090194423233</v>
+        <v>-0.5643987042147999</v>
       </c>
       <c r="I107">
-        <v>-1.131855868547312</v>
+        <v>-1.204575862026376</v>
       </c>
       <c r="J107">
-        <v>0.203675479700846</v>
+        <v>0.07577845359677639</v>
       </c>
       <c r="K107">
-        <v>0.1681011348065048</v>
+        <v>0.08244473405144466</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="M107">
-        <v>0.4622781207178883</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N107">
         <v>11</v>
@@ -5960,25 +5960,25 @@
         <v>46</v>
       </c>
       <c r="E108">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F108">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G108">
-        <v>-0.1060859159529365</v>
+        <v>-0.0336789283299818</v>
       </c>
       <c r="H108">
-        <v>-0.4889098225756967</v>
+        <v>-0.1517418358682805</v>
       </c>
       <c r="I108">
-        <v>-1.156675496699776</v>
+        <v>-0.7919189936798569</v>
       </c>
       <c r="J108">
-        <v>0.1788558515483823</v>
+        <v>0.488435321943296</v>
       </c>
       <c r="K108">
-        <v>0.1469873049490105</v>
+        <v>0.6348832671734959</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="M108">
-        <v>0.4622781207178883</v>
+        <v>0.6983715938908455</v>
       </c>
       <c r="N108">
         <v>11</v>
@@ -6012,25 +6012,25 @@
         <v>44</v>
       </c>
       <c r="E109">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F109">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G109">
-        <v>-1.242641772451081</v>
+        <v>-1.134869417220837</v>
       </c>
       <c r="H109">
-        <v>-0.3085558781659946</v>
+        <v>-0.2815256828166086</v>
       </c>
       <c r="I109">
-        <v>-1.00216770493436</v>
+        <v>-0.9473377722967063</v>
       </c>
       <c r="J109">
-        <v>0.3850559486023706</v>
+        <v>0.3842864066634893</v>
       </c>
       <c r="K109">
-        <v>0.3739890788891871</v>
+        <v>0.3978773870852054</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="M109">
-        <v>0.5531547442458277</v>
+        <v>0.5623900093185237</v>
       </c>
       <c r="N109">
         <v>11</v>
@@ -6064,25 +6064,25 @@
         <v>44</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F110">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G110">
-        <v>3.384294754653697</v>
+        <v>3.21790618353065</v>
       </c>
       <c r="H110">
-        <v>0.4348840337655962</v>
+        <v>0.4133467201847962</v>
       </c>
       <c r="I110">
-        <v>-0.2587277930027689</v>
+        <v>-0.2524653692953018</v>
       </c>
       <c r="J110">
-        <v>1.128495860533961</v>
+        <v>1.079158809664894</v>
       </c>
       <c r="K110">
-        <v>0.2124179010817819</v>
+        <v>0.2168639433216278</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="M110">
-        <v>0.4673193823799203</v>
+        <v>0.4771006753075812</v>
       </c>
       <c r="N110">
         <v>11</v>
@@ -6116,25 +6116,25 @@
         <v>44</v>
       </c>
       <c r="E111">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F111">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G111">
-        <v>151.9783193506986</v>
+        <v>276.4294369820547</v>
       </c>
       <c r="H111">
-        <v>0.1501866354189451</v>
+        <v>0.2748804360866473</v>
       </c>
       <c r="I111">
-        <v>-0.54342519134942</v>
+        <v>-0.3909316533934505</v>
       </c>
       <c r="J111">
-        <v>0.8437984621873104</v>
+        <v>0.940692525566745</v>
       </c>
       <c r="K111">
-        <v>0.66401561675221</v>
+        <v>0.4090109158680172</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="M111">
-        <v>0.757065515062134</v>
+        <v>0.5623900093185237</v>
       </c>
       <c r="N111">
         <v>11</v>
@@ -6165,28 +6165,28 @@
         </is>
       </c>
       <c r="D112">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
       <c r="F112">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G112">
-        <v>0.05299460188663061</v>
+        <v>0.06106561279358888</v>
       </c>
       <c r="H112">
-        <v>0.6529306192059003</v>
+        <v>0.7897168556079338</v>
       </c>
       <c r="I112">
-        <v>-0.1050413388992569</v>
+        <v>0.006253798917781158</v>
       </c>
       <c r="J112">
-        <v>1.410902577311058</v>
+        <v>1.573179912298087</v>
       </c>
       <c r="K112">
-        <v>0.08873165157567806</v>
+        <v>0.0483272459749732</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="M112">
-        <v>0.3110860035036438</v>
+        <v>0.177199901908235</v>
       </c>
       <c r="N112">
         <v>11</v>
@@ -6217,28 +6217,28 @@
         </is>
       </c>
       <c r="D113">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
       <c r="F113">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G113">
-        <v>12.30007453786523</v>
+        <v>16.38361004682843</v>
       </c>
       <c r="H113">
-        <v>0.6049037205937154</v>
+        <v>0.9002156578593844</v>
       </c>
       <c r="I113">
-        <v>-0.1530682375114418</v>
+        <v>0.1167526011692318</v>
       </c>
       <c r="J113">
-        <v>1.362875678698873</v>
+        <v>1.683678714549537</v>
       </c>
       <c r="K113">
-        <v>0.1135905584097008</v>
+        <v>0.02595418483155122</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M113">
-        <v>0.3110860035036438</v>
+        <v>0.177199901908235</v>
       </c>
       <c r="N113">
         <v>11</v>
@@ -6269,28 +6269,28 @@
         </is>
       </c>
       <c r="D114">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E114">
         <v>12</v>
       </c>
       <c r="F114">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G114">
-        <v>3.025491949910553</v>
+        <v>3.237228607918266</v>
       </c>
       <c r="H114">
-        <v>0.5335322933399462</v>
+        <v>0.5660261539323874</v>
       </c>
       <c r="I114">
-        <v>-0.2244396647652111</v>
+        <v>-0.2174369027577653</v>
       </c>
       <c r="J114">
-        <v>1.291504251445103</v>
+        <v>1.34948921062254</v>
       </c>
       <c r="K114">
-        <v>0.1609129702709596</v>
+        <v>0.1495546423601027</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="M114">
-        <v>0.3110860035036438</v>
+        <v>0.2741835109935216</v>
       </c>
       <c r="N114">
         <v>11</v>
@@ -6321,28 +6321,28 @@
         </is>
       </c>
       <c r="D115">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E115">
         <v>12</v>
       </c>
       <c r="F115">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G115">
-        <v>148.9267741377854</v>
+        <v>214.3486776737255</v>
       </c>
       <c r="H115">
-        <v>0.5222216454483343</v>
+        <v>0.8592202741443863</v>
       </c>
       <c r="I115">
-        <v>-0.2357503126568229</v>
+        <v>0.07575721745423372</v>
       </c>
       <c r="J115">
-        <v>1.280193603553492</v>
+        <v>1.642683330834539</v>
       </c>
       <c r="K115">
-        <v>0.1696832746383512</v>
+        <v>0.03282988473752377</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="M115">
-        <v>0.3110860035036438</v>
+        <v>0.177199901908235</v>
       </c>
       <c r="N115">
         <v>11</v>
@@ -6373,28 +6373,28 @@
         </is>
       </c>
       <c r="D116">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E116">
         <v>12</v>
       </c>
       <c r="F116">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G116">
-        <v>-0.02588966328707016</v>
+        <v>-0.04056130029528088</v>
       </c>
       <c r="H116">
-        <v>-0.1341852946951659</v>
+        <v>-0.211089596898243</v>
       </c>
       <c r="I116">
-        <v>-0.8921572528003231</v>
+        <v>-0.9945526535883956</v>
       </c>
       <c r="J116">
-        <v>0.6237866634099913</v>
+        <v>0.5723734597919096</v>
       </c>
       <c r="K116">
-        <v>0.7202241703530645</v>
+        <v>0.5844311925731589</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="M116">
-        <v>0.880273985987079</v>
+        <v>0.8537879706613984</v>
       </c>
       <c r="N116">
         <v>11</v>
@@ -6425,28 +6425,28 @@
         </is>
       </c>
       <c r="D117">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E117">
         <v>12</v>
       </c>
       <c r="F117">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G117">
-        <v>1.401192605843798</v>
+        <v>1.7635163899532</v>
       </c>
       <c r="H117">
-        <v>0.1402343974291386</v>
+        <v>0.1658473129670956</v>
       </c>
       <c r="I117">
-        <v>-0.6177375606760185</v>
+        <v>-0.6176157437230572</v>
       </c>
       <c r="J117">
-        <v>0.8982063555342958</v>
+        <v>0.9493103696572484</v>
       </c>
       <c r="K117">
-        <v>0.7082051107401697</v>
+        <v>0.6670626605646285</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="M117">
-        <v>0.880273985987079</v>
+        <v>0.8537879706613984</v>
       </c>
       <c r="N117">
         <v>11</v>
@@ -6477,28 +6477,28 @@
         </is>
       </c>
       <c r="D118">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E118">
         <v>11</v>
       </c>
       <c r="F118">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G118">
-        <v>0.125500841633978</v>
+        <v>0.03337201512900355</v>
       </c>
       <c r="H118">
-        <v>0.4870889579190145</v>
+        <v>0.1552913417946847</v>
       </c>
       <c r="I118">
-        <v>-0.3054368851237055</v>
+        <v>-0.661093799702828</v>
       </c>
       <c r="J118">
-        <v>1.279614800961735</v>
+        <v>0.9716764832921971</v>
       </c>
       <c r="K118">
-        <v>0.2187820422919906</v>
+        <v>0.6985537941775077</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="M118">
-        <v>0.343800352173128</v>
+        <v>0.8537879706613984</v>
       </c>
       <c r="N118">
         <v>11</v>
@@ -6529,28 +6529,28 @@
         </is>
       </c>
       <c r="D119">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E119">
         <v>11</v>
       </c>
       <c r="F119">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G119">
-        <v>-0.1670578845004275</v>
+        <v>-0.1450201473900723</v>
       </c>
       <c r="H119">
-        <v>-0.8118246858305367</v>
+        <v>-0.7306961803305999</v>
       </c>
       <c r="I119">
-        <v>-1.604350528873257</v>
+        <v>-1.547081321828112</v>
       </c>
       <c r="J119">
-        <v>-0.01929884278781669</v>
+        <v>0.08568896116691258</v>
       </c>
       <c r="K119">
-        <v>0.04501416796805277</v>
+        <v>0.0771625166272437</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="M119">
-        <v>0.3110860035036438</v>
+        <v>0.1935866869760947</v>
       </c>
       <c r="N119">
         <v>11</v>
@@ -6581,28 +6581,28 @@
         </is>
       </c>
       <c r="D120">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
       <c r="F120">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G120">
-        <v>-2.209954154257141</v>
+        <v>-2.247821074567586</v>
       </c>
       <c r="H120">
-        <v>-0.7267627376900192</v>
+        <v>-0.7282402292826939</v>
       </c>
       <c r="I120">
-        <v>-1.552702988624582</v>
+        <v>-1.573342227291149</v>
       </c>
       <c r="J120">
-        <v>0.09917751324454381</v>
+        <v>0.1168617687257613</v>
       </c>
       <c r="K120">
-        <v>0.08216730525885903</v>
+        <v>0.08799394862549759</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="M120">
-        <v>0.3110860035036438</v>
+        <v>0.1935866869760947</v>
       </c>
       <c r="N120">
         <v>11</v>
@@ -6633,28 +6633,28 @@
         </is>
       </c>
       <c r="D121">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E121">
         <v>10</v>
       </c>
       <c r="F121">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G121">
-        <v>-0.03001275452407196</v>
+        <v>0.2989886093678589</v>
       </c>
       <c r="H121">
-        <v>-0.004008482045082379</v>
+        <v>0.03954068202281538</v>
       </c>
       <c r="I121">
-        <v>-0.8299487329796454</v>
+        <v>-0.8055613159856398</v>
       </c>
       <c r="J121">
-        <v>0.8219317688894807</v>
+        <v>0.8846426800312707</v>
       </c>
       <c r="K121">
-        <v>0.9921279999751887</v>
+        <v>0.9238730739622683</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="M121">
-        <v>0.9921279999751887</v>
+        <v>0.9238730739622683</v>
       </c>
       <c r="N121">
         <v>11</v>
@@ -6685,28 +6685,28 @@
         </is>
       </c>
       <c r="D122">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E122">
         <v>10</v>
       </c>
       <c r="F122">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G122">
-        <v>20.16212808192402</v>
+        <v>78.59032819620032</v>
       </c>
       <c r="H122">
-        <v>0.01995651210752262</v>
+        <v>0.07605275881051222</v>
       </c>
       <c r="I122">
-        <v>-0.8059837388270403</v>
+        <v>-0.769049239197943</v>
       </c>
       <c r="J122">
-        <v>0.8458967630420856</v>
+        <v>0.9211547568189674</v>
       </c>
       <c r="K122">
-        <v>0.9608246604122272</v>
+        <v>0.854213289143731</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="M122">
-        <v>0.9921279999751887</v>
+        <v>0.9238730739622683</v>
       </c>
       <c r="N122">
         <v>11</v>
@@ -6737,28 +6737,28 @@
         </is>
       </c>
       <c r="D123">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E123">
         <v>12</v>
       </c>
       <c r="F123">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G123">
-        <v>0.0349345569652896</v>
+        <v>0.02538476673114989</v>
       </c>
       <c r="H123">
-        <v>0.559971868250821</v>
+        <v>0.3916426224468441</v>
       </c>
       <c r="I123">
-        <v>-0.1756820064430566</v>
+        <v>-0.3116971423279121</v>
       </c>
       <c r="J123">
-        <v>1.295625742944698</v>
+        <v>1.0949823872216</v>
       </c>
       <c r="K123">
-        <v>0.1308583467254929</v>
+        <v>0.2662365165137662</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="M123">
-        <v>0.3598604534951055</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N123">
         <v>11</v>
@@ -6789,28 +6789,28 @@
         </is>
       </c>
       <c r="D124">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E124">
         <v>12</v>
       </c>
       <c r="F124">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G124">
-        <v>15.94275362318839</v>
+        <v>11.74233249229041</v>
       </c>
       <c r="H124">
-        <v>0.7711385340171477</v>
+        <v>0.5564323957101016</v>
       </c>
       <c r="I124">
-        <v>0.03548465932327023</v>
+        <v>-0.1469073690646545</v>
       </c>
       <c r="J124">
-        <v>1.506792408711025</v>
+        <v>1.259772160484858</v>
       </c>
       <c r="K124">
-        <v>0.04049997663705954</v>
+        <v>0.1173457785310489</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="M124">
-        <v>0.2088105622605108</v>
+        <v>0.4302678546138458</v>
       </c>
       <c r="N124">
         <v>11</v>
@@ -6841,28 +6841,28 @@
         </is>
       </c>
       <c r="D125">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E125">
         <v>12</v>
       </c>
       <c r="F125">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G125">
-        <v>3.739130434782609</v>
+        <v>3.245164003364169</v>
       </c>
       <c r="H125">
-        <v>0.7132863534163799</v>
+        <v>0.6174805011397217</v>
       </c>
       <c r="I125">
-        <v>-0.02236752127749766</v>
+        <v>-0.08585926363503434</v>
       </c>
       <c r="J125">
-        <v>1.448940228110257</v>
+        <v>1.320820265914478</v>
       </c>
       <c r="K125">
-        <v>0.05694833516195749</v>
+        <v>0.08343246014007469</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="M125">
-        <v>0.2088105622605108</v>
+        <v>0.4302678546138458</v>
       </c>
       <c r="N125">
         <v>11</v>
@@ -6893,28 +6893,28 @@
         </is>
       </c>
       <c r="D126">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E126">
         <v>12</v>
       </c>
       <c r="F126">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G126">
-        <v>38.61539595054657</v>
+        <v>3.457131548782048</v>
       </c>
       <c r="H126">
-        <v>0.1656117637015435</v>
+        <v>0.01510517185702843</v>
       </c>
       <c r="I126">
-        <v>-0.5700421109923339</v>
+        <v>-0.6882345929177276</v>
       </c>
       <c r="J126">
-        <v>0.9012656383954211</v>
+        <v>0.7184449366317845</v>
       </c>
       <c r="K126">
-        <v>0.6496507514854655</v>
+        <v>0.965498976280982</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="M126">
-        <v>0.7149580362777458</v>
+        <v>0.965498976280982</v>
       </c>
       <c r="N126">
         <v>11</v>
@@ -6945,28 +6945,28 @@
         </is>
       </c>
       <c r="D127">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E127">
         <v>12</v>
       </c>
       <c r="F127">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G127">
-        <v>0.07716089621538602</v>
+        <v>0.07328914486530284</v>
       </c>
       <c r="H127">
-        <v>0.337120614330825</v>
+        <v>0.3297109436255405</v>
       </c>
       <c r="I127">
-        <v>-0.3985332603630525</v>
+        <v>-0.3736288211492154</v>
       </c>
       <c r="J127">
-        <v>1.072774489024703</v>
+        <v>1.033050708400296</v>
       </c>
       <c r="K127">
-        <v>0.3575807382315069</v>
+        <v>0.3480820809136316</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M127">
-        <v>0.5619125886495109</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N127">
         <v>11</v>
@@ -6997,28 +6997,28 @@
         </is>
       </c>
       <c r="D128">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E128">
         <v>12</v>
       </c>
       <c r="F128">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G128">
-        <v>5.91413043478263</v>
+        <v>5.39200308382396</v>
       </c>
       <c r="H128">
-        <v>0.5139478541437915</v>
+        <v>0.4945944939953359</v>
       </c>
       <c r="I128">
-        <v>-0.2217060205500859</v>
+        <v>-0.2087452707794201</v>
       </c>
       <c r="J128">
-        <v>1.249601728837669</v>
+        <v>1.197934258770092</v>
       </c>
       <c r="K128">
-        <v>0.1643963426484408</v>
+        <v>0.1624332896759348</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="M128">
-        <v>0.3616719538265698</v>
+        <v>0.4466915466088206</v>
       </c>
       <c r="N128">
         <v>11</v>
@@ -7049,28 +7049,28 @@
         </is>
       </c>
       <c r="D129">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E129">
         <v>11</v>
       </c>
       <c r="F129">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G129">
-        <v>0.2392822365664132</v>
+        <v>0.1167880212851237</v>
       </c>
       <c r="H129">
-        <v>0.9763070462238214</v>
+        <v>0.6703520959641561</v>
       </c>
       <c r="I129">
-        <v>0.2256002091581093</v>
+        <v>-0.05333859559724995</v>
       </c>
       <c r="J129">
-        <v>1.727013883289533</v>
+        <v>1.394042787525562</v>
       </c>
       <c r="K129">
-        <v>0.01248470748797264</v>
+        <v>0.06838484125672245</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="M129">
-        <v>0.1373317823676991</v>
+        <v>0.4302678546138458</v>
       </c>
       <c r="N129">
         <v>11</v>
@@ -7101,28 +7101,28 @@
         </is>
       </c>
       <c r="D130">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E130">
         <v>11</v>
       </c>
       <c r="F130">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G130">
-        <v>-0.04170345187078112</v>
+        <v>-0.07652701128087912</v>
       </c>
       <c r="H130">
-        <v>-0.1686770632402057</v>
+        <v>-0.3091097278546527</v>
       </c>
       <c r="I130">
-        <v>-0.9193839003059177</v>
+        <v>-1.032800419416059</v>
       </c>
       <c r="J130">
-        <v>0.5820297738255064</v>
+        <v>0.4145809637067533</v>
       </c>
       <c r="K130">
-        <v>0.649961851161587</v>
+        <v>0.3917828898263745</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="M130">
-        <v>0.7149580362777458</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N130">
         <v>11</v>
@@ -7153,28 +7153,28 @@
         </is>
       </c>
       <c r="D131">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E131">
         <v>10</v>
       </c>
       <c r="F131">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G131">
-        <v>-0.02097838579320696</v>
+        <v>-0.2866112701395404</v>
       </c>
       <c r="H131">
-        <v>-0.004610983170694543</v>
+        <v>-0.06512952695549454</v>
       </c>
       <c r="I131">
-        <v>-0.7958264193128822</v>
+        <v>-0.8282346744044516</v>
       </c>
       <c r="J131">
-        <v>0.7866044529714931</v>
+        <v>0.6979756204934626</v>
       </c>
       <c r="K131">
-        <v>0.9905718363724141</v>
+        <v>0.8630798485726776</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="M131">
-        <v>0.9905718363724141</v>
+        <v>0.9493878334299455</v>
       </c>
       <c r="N131">
         <v>11</v>
@@ -7205,28 +7205,28 @@
         </is>
       </c>
       <c r="D132">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E132">
         <v>10</v>
       </c>
       <c r="F132">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G132">
-        <v>-3.2471562832674</v>
+        <v>-2.797804334548983</v>
       </c>
       <c r="H132">
-        <v>-0.3649926135508711</v>
+        <v>-0.3215996488025185</v>
       </c>
       <c r="I132">
-        <v>-1.156208049693058</v>
+        <v>-1.084704796251476</v>
       </c>
       <c r="J132">
-        <v>0.4262228225913164</v>
+        <v>0.4415054986464386</v>
       </c>
       <c r="K132">
-        <v>0.3532312742933995</v>
+        <v>0.3970362924744207</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="M132">
-        <v>0.5619125886495109</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N132">
         <v>11</v>
@@ -7257,28 +7257,28 @@
         </is>
       </c>
       <c r="D133">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E133">
         <v>10</v>
       </c>
       <c r="F133">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G133">
-        <v>-241.3066528476148</v>
+        <v>-260.5556418960415</v>
       </c>
       <c r="H133">
-        <v>-0.2597104004425398</v>
+        <v>-0.2869798023850907</v>
       </c>
       <c r="I133">
-        <v>-1.050925836584727</v>
+        <v>-1.050084949834048</v>
       </c>
       <c r="J133">
-        <v>0.5315050356996477</v>
+        <v>0.4761253450638664</v>
       </c>
       <c r="K133">
-        <v>0.5073223878015936</v>
+        <v>0.4492745472140467</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="M133">
-        <v>0.6975682832271911</v>
+        <v>0.5491133354838349</v>
       </c>
       <c r="N133">
         <v>11</v>
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="M2">
-        <v>0.08501431322675891</v>
+        <v>0.1133524176356785</v>
       </c>
       <c r="N2">
         <v>11</v>
       </c>
       <c r="O2">
-        <v>0.09274288715646425</v>
+        <v>0.1236571828752857</v>
       </c>
       <c r="P2">
-        <v>0.06182859143764284</v>
+        <v>0.1228825207777521</v>
       </c>
     </row>
     <row r="3">
@@ -7526,19 +7526,19 @@
         <v>93</v>
       </c>
       <c r="G4">
-        <v>0.1207362841138933</v>
+        <v>0.06714071624716159</v>
       </c>
       <c r="H4">
-        <v>0.6733485374503095</v>
+        <v>0.4405619777979101</v>
       </c>
       <c r="I4">
-        <v>0.2112999839614958</v>
+        <v>-0.02148657569090364</v>
       </c>
       <c r="J4">
-        <v>1.135397090939123</v>
+        <v>0.9026105312867239</v>
       </c>
       <c r="K4">
-        <v>0.004672267809869151</v>
+        <v>0.06144126038887604</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -7546,16 +7546,16 @@
         </is>
       </c>
       <c r="M4">
-        <v>0.03201088303168734</v>
+        <v>0.1436995696814379</v>
       </c>
       <c r="N4">
         <v>11</v>
       </c>
       <c r="O4">
-        <v>0.0186890712394766</v>
+        <v>0.1843237811666281</v>
       </c>
       <c r="P4">
-        <v>0.0186890712394766</v>
+        <v>0.1228825207777521</v>
       </c>
     </row>
     <row r="5">
@@ -7636,25 +7636,25 @@
         <v>93</v>
       </c>
       <c r="E6">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0.01519559416331258</v>
+        <v>0.02289732811964476</v>
       </c>
       <c r="H6">
-        <v>0.2056115766165126</v>
+        <v>0.3117763169211952</v>
       </c>
       <c r="I6">
-        <v>-0.2558985978551914</v>
+        <v>-0.1400463604782532</v>
       </c>
       <c r="J6">
-        <v>0.6671217510882165</v>
+        <v>0.7635989943206437</v>
       </c>
       <c r="K6">
-        <v>0.3782691358385621</v>
+        <v>0.1737072849770679</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         </is>
       </c>
       <c r="M6">
-        <v>0.5944229277463119</v>
+        <v>0.2811892457359251</v>
       </c>
       <c r="N6">
         <v>11</v>
       </c>
       <c r="O6">
-        <v>0.7565382716771243</v>
+        <v>0.5211218549312038</v>
       </c>
       <c r="P6">
-        <v>0.5043588477847495</v>
+        <v>0.2385848145638153</v>
       </c>
     </row>
     <row r="7">
@@ -7694,25 +7694,25 @@
         <v>92</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>-0.1590767094656389</v>
+        <v>-0.161300334277039</v>
       </c>
       <c r="H7">
-        <v>-0.6741524908503982</v>
+        <v>-0.6860428340463276</v>
       </c>
       <c r="I7">
-        <v>-1.138670216172327</v>
+        <v>-1.140689678068461</v>
       </c>
       <c r="J7">
-        <v>-0.2096347655284691</v>
+        <v>-0.2313959900241943</v>
       </c>
       <c r="K7">
-        <v>0.004951000691451968</v>
+        <v>0.003539592810587274</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -7720,16 +7720,16 @@
         </is>
       </c>
       <c r="M7">
-        <v>0.05446100760597165</v>
+        <v>0.03893552091646001</v>
       </c>
       <c r="N7">
         <v>11</v>
       </c>
       <c r="O7">
-        <v>0.01980400276580787</v>
+        <v>0.0141583712423491</v>
       </c>
       <c r="P7">
-        <v>0.01980400276580787</v>
+        <v>0.0141583712423491</v>
       </c>
     </row>
     <row r="8">
@@ -7752,25 +7752,25 @@
         <v>93</v>
       </c>
       <c r="E8">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>-0.01955974549781864</v>
+        <v>-0.02915969001335296</v>
       </c>
       <c r="H8">
-        <v>-0.1365500805604654</v>
+        <v>-0.2041111658505001</v>
       </c>
       <c r="I8">
-        <v>-0.5980602550321693</v>
+        <v>-0.6559338432499485</v>
       </c>
       <c r="J8">
-        <v>0.3249600939112386</v>
+        <v>0.2477115115489483</v>
       </c>
       <c r="K8">
-        <v>0.5579507677338391</v>
+        <v>0.3716660196807224</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -7778,16 +7778,16 @@
         </is>
       </c>
       <c r="M8">
-        <v>0.613745844507223</v>
+        <v>0.5110407770609934</v>
       </c>
       <c r="N8">
         <v>11</v>
       </c>
       <c r="O8">
-        <v>0.7565382716771243</v>
+        <v>0.5211218549312038</v>
       </c>
       <c r="P8">
-        <v>0.5579507677338391</v>
+        <v>0.3716660196807224</v>
       </c>
     </row>
     <row r="9">
@@ -7810,25 +7810,25 @@
         <v>91</v>
       </c>
       <c r="E9">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G9">
-        <v>-1.153398341440845</v>
+        <v>-1.103575744358542</v>
       </c>
       <c r="H9">
-        <v>-0.3283223346682714</v>
+        <v>-0.313968545412381</v>
       </c>
       <c r="I9">
-        <v>-0.798201162611234</v>
+        <v>-0.7746316821981623</v>
       </c>
       <c r="J9">
-        <v>0.1415564932746911</v>
+        <v>0.1466945913734004</v>
       </c>
       <c r="K9">
-        <v>0.1683474985975603</v>
+        <v>0.1789386109228615</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="M9">
-        <v>0.4629556211432908</v>
+        <v>0.2811892457359251</v>
       </c>
       <c r="N9">
         <v>11</v>
       </c>
       <c r="O9">
-        <v>0.5050424957926809</v>
+        <v>0.5211218549312038</v>
       </c>
       <c r="P9">
-        <v>0.3366949971951206</v>
+        <v>0.2385848145638153</v>
       </c>
     </row>
     <row r="10">
@@ -7865,28 +7865,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>0.04437100172332005</v>
+        <v>0.04826649997748613</v>
       </c>
       <c r="H10">
-        <v>0.5479113482978304</v>
+        <v>0.6093470224184824</v>
       </c>
       <c r="I10">
-        <v>0.008758542538902627</v>
+        <v>0.06176451071040267</v>
       </c>
       <c r="J10">
-        <v>1.087064154056758</v>
+        <v>1.156929534126562</v>
       </c>
       <c r="K10">
-        <v>0.04651350775014364</v>
+        <v>0.02987943506650974</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -7894,16 +7894,16 @@
         </is>
       </c>
       <c r="M10">
-        <v>0.2182628643343841</v>
+        <v>0.1095579285772024</v>
       </c>
       <c r="N10">
         <v>11</v>
       </c>
       <c r="O10">
-        <v>0.1860540310005746</v>
+        <v>0.119517740266039</v>
       </c>
       <c r="P10">
-        <v>0.1529474124701516</v>
+        <v>0.119517740266039</v>
       </c>
     </row>
     <row r="11">
@@ -7923,28 +7923,28 @@
         </is>
       </c>
       <c r="D11">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G11">
-        <v>-0.08389511077681858</v>
+        <v>-0.09312397376822193</v>
       </c>
       <c r="H11">
-        <v>-0.3566984237544505</v>
+        <v>-0.3923478690519177</v>
       </c>
       <c r="I11">
-        <v>-0.8984512233319308</v>
+        <v>-0.942675367532973</v>
       </c>
       <c r="J11">
-        <v>0.1850543758230297</v>
+        <v>0.1579796294291377</v>
       </c>
       <c r="K11">
-        <v>0.1924705350545534</v>
+        <v>0.1584504734730672</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -7952,16 +7952,16 @@
         </is>
       </c>
       <c r="M11">
-        <v>0.3528626476000146</v>
+        <v>0.3485910416407478</v>
       </c>
       <c r="N11">
         <v>11</v>
       </c>
       <c r="O11">
-        <v>0.3849410701091068</v>
+        <v>0.4753514204192015</v>
       </c>
       <c r="P11">
-        <v>0.2566273800727379</v>
+        <v>0.3169009469461344</v>
       </c>
     </row>
     <row r="12">
@@ -7981,28 +7981,28 @@
         </is>
       </c>
       <c r="D12">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>23</v>
       </c>
       <c r="F12">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G12">
-        <v>0.09914571935849043</v>
+        <v>0.05312458313744517</v>
       </c>
       <c r="H12">
-        <v>0.4968443794342607</v>
+        <v>0.3189302287555219</v>
       </c>
       <c r="I12">
-        <v>-0.05464228611951752</v>
+        <v>-0.2398164103865086</v>
       </c>
       <c r="J12">
-        <v>1.048331044988039</v>
+        <v>0.8776768678975525</v>
       </c>
       <c r="K12">
-        <v>0.07647370623507579</v>
+        <v>0.2571766374667313</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -8010,16 +8010,16 @@
         </is>
       </c>
       <c r="M12">
-        <v>0.2182628643343841</v>
+        <v>0.4688445860254871</v>
       </c>
       <c r="N12">
         <v>11</v>
       </c>
       <c r="O12">
-        <v>0.2294211187052274</v>
+        <v>0.5143532749334625</v>
       </c>
       <c r="P12">
-        <v>0.1529474124701516</v>
+        <v>0.3409778807458088</v>
       </c>
     </row>
     <row r="13">
@@ -8039,28 +8039,28 @@
         </is>
       </c>
       <c r="D13">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>22</v>
       </c>
       <c r="F13">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G13">
-        <v>-0.8738223763184577</v>
+        <v>-0.8697518663723902</v>
       </c>
       <c r="H13">
-        <v>-0.2756315959506122</v>
+        <v>-0.2718189261208896</v>
       </c>
       <c r="I13">
-        <v>-0.8380837624221419</v>
+        <v>-0.8397040227039787</v>
       </c>
       <c r="J13">
-        <v>0.2868205705209176</v>
+        <v>0.2960661704621995</v>
       </c>
       <c r="K13">
-        <v>0.3301113930012022</v>
+        <v>0.3409778807458088</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -8068,16 +8068,16 @@
         </is>
       </c>
       <c r="M13">
-        <v>0.453903165376653</v>
+        <v>0.4688445860254871</v>
       </c>
       <c r="N13">
         <v>11</v>
       </c>
       <c r="O13">
-        <v>0.3849410701091068</v>
+        <v>0.5143532749334625</v>
       </c>
       <c r="P13">
-        <v>0.3301113930012022</v>
+        <v>0.3409778807458088</v>
       </c>
     </row>
     <row r="14">
@@ -8097,28 +8097,28 @@
         </is>
       </c>
       <c r="D14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E14">
         <v>24</v>
       </c>
       <c r="F14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G14">
-        <v>0.03547313223364898</v>
+        <v>0.03070908131374459</v>
       </c>
       <c r="H14">
-        <v>0.5564992230321598</v>
+        <v>0.4733649834777794</v>
       </c>
       <c r="I14">
-        <v>0.05944752886453677</v>
+        <v>-0.01352140033195895</v>
       </c>
       <c r="J14">
-        <v>1.053550917199783</v>
+        <v>0.9602513672875178</v>
       </c>
       <c r="K14">
-        <v>0.02874273227742575</v>
+        <v>0.05653917068926837</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -8126,16 +8126,16 @@
         </is>
       </c>
       <c r="M14">
-        <v>0.0790425137629208</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N14">
         <v>11</v>
       </c>
       <c r="O14">
-        <v>0.08622819683227724</v>
+        <v>0.2047361257399495</v>
       </c>
       <c r="P14">
-        <v>0.05748546455485149</v>
+        <v>0.1130783413785367</v>
       </c>
     </row>
     <row r="15">
@@ -8155,28 +8155,28 @@
         </is>
       </c>
       <c r="D15">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E15">
         <v>24</v>
       </c>
       <c r="F15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G15">
-        <v>0.05654488213554677</v>
+        <v>0.05541989464635406</v>
       </c>
       <c r="H15">
-        <v>0.2188999448996439</v>
+        <v>0.218182585781288</v>
       </c>
       <c r="I15">
-        <v>-0.2781517492679793</v>
+        <v>-0.2687037980284504</v>
       </c>
       <c r="J15">
-        <v>0.7159516390672669</v>
+        <v>0.7050689695910263</v>
       </c>
       <c r="K15">
-        <v>0.3828372552862699</v>
+        <v>0.3748748589945128</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -8184,16 +8184,16 @@
         </is>
       </c>
       <c r="M15">
-        <v>0.467912200905441</v>
+        <v>0.4581803832155157</v>
       </c>
       <c r="N15">
         <v>11</v>
       </c>
       <c r="O15">
-        <v>0.7656745105725398</v>
+        <v>0.7497497179890256</v>
       </c>
       <c r="P15">
-        <v>0.5104496737150265</v>
+        <v>0.499833145326017</v>
       </c>
     </row>
     <row r="16">
@@ -8213,28 +8213,28 @@
         </is>
       </c>
       <c r="D16">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E16">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G16">
-        <v>0.1312496070497738</v>
+        <v>0.07533161201871862</v>
       </c>
       <c r="H16">
-        <v>0.6711483926699491</v>
+        <v>0.4910137319917606</v>
       </c>
       <c r="I16">
-        <v>0.1695004090975513</v>
+        <v>-0.002592081012958921</v>
       </c>
       <c r="J16">
-        <v>1.172796376242347</v>
+        <v>0.9846195449964801</v>
       </c>
       <c r="K16">
-        <v>0.009465351071373442</v>
+        <v>0.05118403143498738</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -8242,16 +8242,16 @@
         </is>
       </c>
       <c r="M16">
-        <v>0.06988879979866715</v>
+        <v>0.155482719395488</v>
       </c>
       <c r="N16">
         <v>11</v>
       </c>
       <c r="O16">
-        <v>0.03786140428549377</v>
+        <v>0.2047361257399495</v>
       </c>
       <c r="P16">
-        <v>0.03786140428549377</v>
+        <v>0.1130783413785367</v>
       </c>
     </row>
     <row r="17">
@@ -8271,28 +8271,28 @@
         </is>
       </c>
       <c r="D17">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>22</v>
       </c>
       <c r="F17">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G17">
-        <v>0.6186613956330169</v>
+        <v>0.4787257317160428</v>
       </c>
       <c r="H17">
-        <v>0.1604499623693021</v>
+        <v>0.1254953220585758</v>
       </c>
       <c r="I17">
-        <v>-0.3529395843647835</v>
+        <v>-0.3801389480648064</v>
       </c>
       <c r="J17">
-        <v>0.6738395091033877</v>
+        <v>0.6311295921819581</v>
       </c>
       <c r="K17">
-        <v>0.5349470753598955</v>
+        <v>0.6222096669098827</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -8300,16 +8300,16 @@
         </is>
       </c>
       <c r="M17">
-        <v>0.5884417828958851</v>
+        <v>0.684430633600871</v>
       </c>
       <c r="N17">
         <v>11</v>
       </c>
       <c r="O17">
-        <v>0.7656745105725398</v>
+        <v>0.7497497179890256</v>
       </c>
       <c r="P17">
-        <v>0.5349470753598955</v>
+        <v>0.6222096669098827</v>
       </c>
     </row>
     <row r="18">
@@ -9286,16 +9286,16 @@
         </is>
       </c>
       <c r="M34">
-        <v>0.3377491165742667</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N34">
         <v>11</v>
       </c>
       <c r="O34">
-        <v>0.3684535817173818</v>
+        <v>0.4912714422898424</v>
       </c>
       <c r="P34">
-        <v>0.2456357211449212</v>
+        <v>0.3383047061599109</v>
       </c>
     </row>
     <row r="35">
@@ -9382,19 +9382,19 @@
         <v>46</v>
       </c>
       <c r="G36">
-        <v>0.1957187609337613</v>
+        <v>0.08418893637299102</v>
       </c>
       <c r="H36">
-        <v>0.8850864177982237</v>
+        <v>0.4687775347318363</v>
       </c>
       <c r="I36">
-        <v>0.2105613513849146</v>
+        <v>-0.2057475316814728</v>
       </c>
       <c r="J36">
-        <v>1.559611484211533</v>
+        <v>1.143302601145145</v>
       </c>
       <c r="K36">
-        <v>0.01109824932238578</v>
+        <v>0.1691523530799554</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -9402,16 +9402,16 @@
         </is>
       </c>
       <c r="M36">
-        <v>0.1220807425462435</v>
+        <v>0.3921829651322529</v>
       </c>
       <c r="N36">
         <v>11</v>
       </c>
       <c r="O36">
-        <v>0.0443929972895431</v>
+        <v>0.5074570592398663</v>
       </c>
       <c r="P36">
-        <v>0.0443929972895431</v>
+        <v>0.3383047061599109</v>
       </c>
     </row>
     <row r="37">
@@ -9492,25 +9492,25 @@
         <v>46</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F38">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G38">
-        <v>0.02592323580526977</v>
+        <v>0.04005817128712362</v>
       </c>
       <c r="H38">
-        <v>0.3454707593674134</v>
+        <v>0.5452702075255837</v>
       </c>
       <c r="I38">
-        <v>-0.3222949147566656</v>
+        <v>-0.09490695028599257</v>
       </c>
       <c r="J38">
-        <v>1.013236433491493</v>
+        <v>1.18544736533716</v>
       </c>
       <c r="K38">
-        <v>0.3024293571914576</v>
+        <v>0.09299647934519963</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -9518,16 +9518,16 @@
         </is>
       </c>
       <c r="M38">
-        <v>0.5531547442458277</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N38">
         <v>11</v>
       </c>
       <c r="O38">
-        <v>0.6048587143829153</v>
+        <v>0.3297789362057786</v>
       </c>
       <c r="P38">
-        <v>0.3739890788891871</v>
+        <v>0.1239953057935995</v>
       </c>
     </row>
     <row r="39">
@@ -9550,25 +9550,25 @@
         <v>46</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G39">
-        <v>-0.1070894661822752</v>
+        <v>-0.1155758292170839</v>
       </c>
       <c r="H39">
-        <v>-0.5130962350534849</v>
+        <v>-0.5580435774555059</v>
       </c>
       <c r="I39">
-        <v>-1.180861909177564</v>
+        <v>-1.198220735267082</v>
       </c>
       <c r="J39">
-        <v>0.154669439070594</v>
+        <v>0.08213358035607042</v>
       </c>
       <c r="K39">
-        <v>0.128489258634602</v>
+        <v>0.08583307022047661</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -9576,16 +9576,16 @@
         </is>
       </c>
       <c r="M39">
-        <v>0.4622781207178883</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N39">
         <v>11</v>
       </c>
       <c r="O39">
-        <v>0.5139570345384081</v>
+        <v>0.3297789362057786</v>
       </c>
       <c r="P39">
-        <v>0.3362022696130096</v>
+        <v>0.1239953057935995</v>
       </c>
     </row>
     <row r="40">
@@ -9608,25 +9608,25 @@
         <v>46</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F40">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G40">
-        <v>-0.07222996891840137</v>
+        <v>-0.08666853877123173</v>
       </c>
       <c r="H40">
-        <v>-0.464090194423233</v>
+        <v>-0.5643987042147999</v>
       </c>
       <c r="I40">
-        <v>-1.131855868547312</v>
+        <v>-1.204575862026376</v>
       </c>
       <c r="J40">
-        <v>0.203675479700846</v>
+        <v>0.07577845359677639</v>
       </c>
       <c r="K40">
-        <v>0.1681011348065048</v>
+        <v>0.08244473405144466</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -9634,16 +9634,16 @@
         </is>
       </c>
       <c r="M40">
-        <v>0.4622781207178883</v>
+        <v>0.255740318199299</v>
       </c>
       <c r="N40">
         <v>11</v>
       </c>
       <c r="O40">
-        <v>0.5139570345384081</v>
+        <v>0.3297789362057786</v>
       </c>
       <c r="P40">
-        <v>0.3362022696130096</v>
+        <v>0.1239953057935995</v>
       </c>
     </row>
     <row r="41">
@@ -9666,25 +9666,25 @@
         <v>44</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F41">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G41">
-        <v>-1.242641772451081</v>
+        <v>-1.134869417220837</v>
       </c>
       <c r="H41">
-        <v>-0.3085558781659946</v>
+        <v>-0.2815256828166086</v>
       </c>
       <c r="I41">
-        <v>-1.00216770493436</v>
+        <v>-0.9473377722967063</v>
       </c>
       <c r="J41">
-        <v>0.3850559486023706</v>
+        <v>0.3842864066634893</v>
       </c>
       <c r="K41">
-        <v>0.3739890788891871</v>
+        <v>0.3978773870852054</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -9692,16 +9692,16 @@
         </is>
       </c>
       <c r="M41">
-        <v>0.5531547442458277</v>
+        <v>0.5623900093185237</v>
       </c>
       <c r="N41">
         <v>11</v>
       </c>
       <c r="O41">
-        <v>0.6048587143829153</v>
+        <v>0.3978773870852054</v>
       </c>
       <c r="P41">
-        <v>0.3739890788891871</v>
+        <v>0.3978773870852054</v>
       </c>
     </row>
     <row r="42">
@@ -9721,28 +9721,28 @@
         </is>
       </c>
       <c r="D42">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E42">
         <v>12</v>
       </c>
       <c r="F42">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G42">
-        <v>0.05299460188663061</v>
+        <v>0.06106561279358888</v>
       </c>
       <c r="H42">
-        <v>0.6529306192059003</v>
+        <v>0.7897168556079338</v>
       </c>
       <c r="I42">
-        <v>-0.1050413388992569</v>
+        <v>0.006253798917781158</v>
       </c>
       <c r="J42">
-        <v>1.410902577311058</v>
+        <v>1.573179912298087</v>
       </c>
       <c r="K42">
-        <v>0.08873165157567806</v>
+        <v>0.0483272459749732</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -9750,16 +9750,16 @@
         </is>
       </c>
       <c r="M42">
-        <v>0.3110860035036438</v>
+        <v>0.177199901908235</v>
       </c>
       <c r="N42">
         <v>11</v>
       </c>
       <c r="O42">
-        <v>0.3286692210354361</v>
+        <v>0.1933089838998928</v>
       </c>
       <c r="P42">
-        <v>0.1774633031513561</v>
+        <v>0.1759878972509952</v>
       </c>
     </row>
     <row r="43">
@@ -9779,28 +9779,28 @@
         </is>
       </c>
       <c r="D43">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="F43">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G43">
-        <v>-0.02588966328707016</v>
+        <v>-0.04056130029528088</v>
       </c>
       <c r="H43">
-        <v>-0.1341852946951659</v>
+        <v>-0.211089596898243</v>
       </c>
       <c r="I43">
-        <v>-0.8921572528003231</v>
+        <v>-0.9945526535883956</v>
       </c>
       <c r="J43">
-        <v>0.6237866634099913</v>
+        <v>0.5723734597919096</v>
       </c>
       <c r="K43">
-        <v>0.7202241703530645</v>
+        <v>0.5844311925731589</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -9808,16 +9808,16 @@
         </is>
       </c>
       <c r="M43">
-        <v>0.880273985987079</v>
+        <v>0.8537879706613984</v>
       </c>
       <c r="N43">
         <v>11</v>
       </c>
       <c r="O43">
-        <v>0.7202241703530645</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>0.7202241703530645</v>
+        <v>0.6985537941775077</v>
       </c>
     </row>
     <row r="44">
@@ -9837,28 +9837,28 @@
         </is>
       </c>
       <c r="D44">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G44">
-        <v>0.125500841633978</v>
+        <v>0.03337201512900355</v>
       </c>
       <c r="H44">
-        <v>0.4870889579190145</v>
+        <v>0.1552913417946847</v>
       </c>
       <c r="I44">
-        <v>-0.3054368851237055</v>
+        <v>-0.661093799702828</v>
       </c>
       <c r="J44">
-        <v>1.279614800961735</v>
+        <v>0.9716764832921971</v>
       </c>
       <c r="K44">
-        <v>0.2187820422919906</v>
+        <v>0.6985537941775077</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -9866,16 +9866,16 @@
         </is>
       </c>
       <c r="M44">
-        <v>0.343800352173128</v>
+        <v>0.8537879706613984</v>
       </c>
       <c r="N44">
         <v>11</v>
       </c>
       <c r="O44">
-        <v>0.4375640845839811</v>
+        <v>1</v>
       </c>
       <c r="P44">
-        <v>0.291709389722654</v>
+        <v>0.6985537941775077</v>
       </c>
     </row>
     <row r="45">
@@ -9895,28 +9895,28 @@
         </is>
       </c>
       <c r="D45">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G45">
-        <v>-2.209954154257141</v>
+        <v>-2.247821074567586</v>
       </c>
       <c r="H45">
-        <v>-0.7267627376900192</v>
+        <v>-0.7282402292826939</v>
       </c>
       <c r="I45">
-        <v>-1.552702988624582</v>
+        <v>-1.573342227291149</v>
       </c>
       <c r="J45">
-        <v>0.09917751324454381</v>
+        <v>0.1168617687257613</v>
       </c>
       <c r="K45">
-        <v>0.08216730525885903</v>
+        <v>0.08799394862549759</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -9924,16 +9924,16 @@
         </is>
       </c>
       <c r="M45">
-        <v>0.3110860035036438</v>
+        <v>0.1935866869760947</v>
       </c>
       <c r="N45">
         <v>11</v>
       </c>
       <c r="O45">
-        <v>0.3286692210354361</v>
+        <v>0.2639818458764928</v>
       </c>
       <c r="P45">
-        <v>0.1774633031513561</v>
+        <v>0.1759878972509952</v>
       </c>
     </row>
     <row r="46">
@@ -9953,28 +9953,28 @@
         </is>
       </c>
       <c r="D46">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E46">
         <v>12</v>
       </c>
       <c r="F46">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G46">
-        <v>0.0349345569652896</v>
+        <v>0.02538476673114989</v>
       </c>
       <c r="H46">
-        <v>0.559971868250821</v>
+        <v>0.3916426224468441</v>
       </c>
       <c r="I46">
-        <v>-0.1756820064430566</v>
+        <v>-0.3116971423279121</v>
       </c>
       <c r="J46">
-        <v>1.295625742944698</v>
+        <v>1.0949823872216</v>
       </c>
       <c r="K46">
-        <v>0.1308583467254929</v>
+        <v>0.2662365165137662</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -9982,16 +9982,16 @@
         </is>
       </c>
       <c r="M46">
-        <v>0.3598604534951055</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N46">
         <v>11</v>
       </c>
       <c r="O46">
-        <v>0.3925750401764788</v>
+        <v>0.7987095495412986</v>
       </c>
       <c r="P46">
-        <v>0.2617166934509859</v>
+        <v>0.4641094412181754</v>
       </c>
     </row>
     <row r="47">
@@ -10011,28 +10011,28 @@
         </is>
       </c>
       <c r="D47">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E47">
         <v>12</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G47">
-        <v>0.07716089621538602</v>
+        <v>0.07328914486530284</v>
       </c>
       <c r="H47">
-        <v>0.337120614330825</v>
+        <v>0.3297109436255405</v>
       </c>
       <c r="I47">
-        <v>-0.3985332603630525</v>
+        <v>-0.3736288211492154</v>
       </c>
       <c r="J47">
-        <v>1.072774489024703</v>
+        <v>1.033050708400296</v>
       </c>
       <c r="K47">
-        <v>0.3575807382315069</v>
+        <v>0.3480820809136316</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -10040,16 +10040,16 @@
         </is>
       </c>
       <c r="M47">
-        <v>0.5619125886495109</v>
+        <v>0.5459249021523285</v>
       </c>
       <c r="N47">
         <v>11</v>
       </c>
       <c r="O47">
-        <v>0.7151614764630139</v>
+        <v>0.7987095495412986</v>
       </c>
       <c r="P47">
-        <v>0.4767743176420092</v>
+        <v>0.4641094412181754</v>
       </c>
     </row>
     <row r="48">
@@ -10069,28 +10069,28 @@
         </is>
       </c>
       <c r="D48">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E48">
         <v>11</v>
       </c>
       <c r="F48">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>0.2392822365664132</v>
+        <v>0.1167880212851237</v>
       </c>
       <c r="H48">
-        <v>0.9763070462238214</v>
+        <v>0.6703520959641561</v>
       </c>
       <c r="I48">
-        <v>0.2256002091581093</v>
+        <v>-0.05333859559724995</v>
       </c>
       <c r="J48">
-        <v>1.727013883289533</v>
+        <v>1.394042787525562</v>
       </c>
       <c r="K48">
-        <v>0.01248470748797264</v>
+        <v>0.06838484125672245</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -10098,16 +10098,16 @@
         </is>
       </c>
       <c r="M48">
-        <v>0.1373317823676991</v>
+        <v>0.4302678546138458</v>
       </c>
       <c r="N48">
         <v>11</v>
       </c>
       <c r="O48">
-        <v>0.04993882995189058</v>
+        <v>0.2735393650268898</v>
       </c>
       <c r="P48">
-        <v>0.04993882995189058</v>
+        <v>0.2735393650268898</v>
       </c>
     </row>
     <row r="49">
@@ -10127,28 +10127,28 @@
         </is>
       </c>
       <c r="D49">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E49">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G49">
-        <v>-0.02097838579320696</v>
+        <v>-0.2866112701395404</v>
       </c>
       <c r="H49">
-        <v>-0.004610983170694543</v>
+        <v>-0.06512952695549454</v>
       </c>
       <c r="I49">
-        <v>-0.7958264193128822</v>
+        <v>-0.8282346744044516</v>
       </c>
       <c r="J49">
-        <v>0.7866044529714931</v>
+        <v>0.6979756204934626</v>
       </c>
       <c r="K49">
-        <v>0.9905718363724141</v>
+        <v>0.8630798485726776</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -10156,16 +10156,16 @@
         </is>
       </c>
       <c r="M49">
-        <v>0.9905718363724141</v>
+        <v>0.9493878334299455</v>
       </c>
       <c r="N49">
         <v>11</v>
       </c>
       <c r="O49">
-        <v>0.9905718363724141</v>
+        <v>0.8630798485726776</v>
       </c>
       <c r="P49">
-        <v>0.9905718363724141</v>
+        <v>0.8630798485726776</v>
       </c>
     </row>
   </sheetData>
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6111441083903314</v>
+        <v>0.2315310456982411</v>
       </c>
       <c r="C2">
-        <v>0.7469539102548496</v>
+        <v>0.5093683005361305</v>
       </c>
     </row>
     <row r="3">
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.05013100428874794</v>
+        <v>0.4195961967874204</v>
       </c>
       <c r="C3">
-        <v>0.3496544021072502</v>
+        <v>0.6251511240017139</v>
       </c>
     </row>
     <row r="4">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8284051268156475</v>
+        <v>0.8511448756348129</v>
       </c>
       <c r="C4">
-        <v>0.8284051268156475</v>
+        <v>0.9362593631982943</v>
       </c>
     </row>
     <row r="5">
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1935637712238565</v>
+        <v>0.01218891999913661</v>
       </c>
       <c r="C5">
-        <v>0.3496544021072502</v>
+        <v>0.1340781199905027</v>
       </c>
     </row>
     <row r="6">
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1808619242264936</v>
+        <v>0.366507550440218</v>
       </c>
       <c r="C6">
-        <v>0.3496544021072502</v>
+        <v>0.6251511240017139</v>
       </c>
     </row>
     <row r="7">
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.2225073467955228</v>
+        <v>0.170397654849191</v>
       </c>
       <c r="C7">
-        <v>0.3496544021072502</v>
+        <v>0.4685935508352753</v>
       </c>
     </row>
     <row r="8">
@@ -10280,10 +10280,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.139572269863044</v>
+        <v>0.06048423243357975</v>
       </c>
       <c r="C8">
-        <v>0.3496544021072502</v>
+        <v>0.3326632783846887</v>
       </c>
     </row>
     <row r="9">
@@ -10293,10 +10293,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.2192917378688993</v>
+        <v>0.4546553629103374</v>
       </c>
       <c r="C9">
-        <v>0.3496544021072502</v>
+        <v>0.6251511240017139</v>
       </c>
     </row>
     <row r="10">
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.8268681089981347</v>
+        <v>0.9374580154641129</v>
       </c>
       <c r="C10">
-        <v>0.8284051268156475</v>
+        <v>0.9374580154641129</v>
       </c>
     </row>
     <row r="11">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.4811255600551847</v>
+        <v>0.5487835350930421</v>
       </c>
       <c r="C11">
-        <v>0.6615476450758789</v>
+        <v>0.6707354317803849</v>
       </c>
     </row>
     <row r="12">
@@ -10332,10 +10332,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.2107840501595656</v>
+        <v>0.09906788840545186</v>
       </c>
       <c r="C12">
-        <v>0.3496544021072502</v>
+        <v>0.3632489241533235</v>
       </c>
     </row>
   </sheetData>
